--- a/AAII_Financials/Quarterly/BICEY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BICEY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="92">
   <si>
     <t>BICEY</t>
   </si>
@@ -656,81 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +781,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,8 +831,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +881,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +905,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -923,8 +951,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,8 +1001,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,8 +1051,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1055,8 +1101,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,8 +1122,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1114,8 +1168,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1158,8 +1218,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,8 +1242,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1220,8 +1288,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1264,8 +1338,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1308,8 +1388,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1352,8 +1438,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1396,8 +1488,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,8 +1538,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1484,8 +1588,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1528,8 +1638,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1688,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1738,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1788,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,8 +1838,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1748,8 +1888,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1792,8 +1938,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,8 +1988,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1880,57 +2038,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2117,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,272 +2137,310 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>487900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>492400</v>
+      </c>
+      <c r="F41" s="3">
         <v>541300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>540900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>364200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>335200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>472100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>412900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>517000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>357200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>444900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>326300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>357200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>322800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>444900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F42" s="3">
         <v>9400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>10600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>14200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>7000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>14200</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>686300</v>
+      </c>
+      <c r="F43" s="3">
         <v>495300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>494900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>686400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>631700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>472500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>619200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>446000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>629800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>443200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>629800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>443200</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>581400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>586700</v>
+      </c>
+      <c r="F44" s="3">
         <v>560800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>560400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>624500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>574800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>557600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>597400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>616800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>655700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>628700</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>655700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>628700</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>77800</v>
+      </c>
+      <c r="F45" s="3">
         <v>93400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>93300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>84100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>77400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>57600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>38800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>56200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>49100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>78200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>878500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>49100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1366000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>78200</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1836500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1853400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1700200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1699000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1763100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1622700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1563000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1670300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1646500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1706000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1602000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1204800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1706000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1688800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1602000</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2273,96 +2483,114 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>669500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>675600</v>
+      </c>
+      <c r="F48" s="3">
         <v>692800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>692400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>685200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>630600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>631500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>643100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>689100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>663100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>654700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>663100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>654700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>483900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>488400</v>
+      </c>
+      <c r="F49" s="3">
         <v>489600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>489200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>595000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>547600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>570100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>414900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>422000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>435400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>434500</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>435400</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>434500</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2633,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,52 +2683,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F52" s="3">
         <v>32600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>32600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>32700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>30100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>32200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>39100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>39000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>33900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>37200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1654500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>33900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1271500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2783,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3176000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3205300</v>
+      </c>
+      <c r="F54" s="3">
         <v>3068400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3066200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3212600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2956700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2934600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2894200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2926200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2964500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2871000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2859300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2964500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2960300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2871000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2857,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,216 +2877,242 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>213600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>215600</v>
+      </c>
+      <c r="F57" s="3">
         <v>179900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>179800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>214500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>197400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>179000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>194700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>159900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>206100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>193600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>206100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>203100</v>
+      </c>
+      <c r="F58" s="3">
         <v>192100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>192000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>223800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>206000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>173300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>153300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>120900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>174900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>81800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>174900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>81800</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>265500</v>
+      </c>
+      <c r="F59" s="3">
         <v>212300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>212100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>257200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>236700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>229400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>138600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>246400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>126900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>257200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>681000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>126900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>673900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>257200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>830800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>838500</v>
+      </c>
+      <c r="F60" s="3">
         <v>702500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>702000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>825900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>760100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>708800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>736400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>648100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>756800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>646700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>681000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>756800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>673900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>646700</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>181500</v>
+      </c>
+      <c r="F61" s="3">
         <v>180700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>180500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>204800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>188500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>173400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>46000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>51700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>45800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>45800</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>45800</v>
@@ -2837,52 +3123,64 @@
       <c r="P61" s="3">
         <v>45800</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>121900</v>
+      </c>
+      <c r="F62" s="3">
         <v>145500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>145400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>88000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>81000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>78400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>66900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>60700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>57500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>44800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>218000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>57500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>216900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>44800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3223,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3273,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3323,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1213800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1225000</v>
+      </c>
+      <c r="F66" s="3">
         <v>1113700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1112900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1240700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1141900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1078000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>959200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>885100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>976000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>876800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>899000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>976000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>890800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>876800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3397,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3443,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3493,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3543,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3593,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2008500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2027000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2049500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2048100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2076400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1911000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1893800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1956800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2035800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2010900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1861100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>2010900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>1861100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3693,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3743,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3793,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1980200</v>
+      </c>
+      <c r="F76" s="3">
         <v>1954600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1953300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1971900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1814800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1856600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1935100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2041100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1988600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1994200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1960300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1988600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2069500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1994200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,57 +3893,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3608,8 +3998,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,16 +4022,18 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>30700</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
@@ -3670,8 +4068,14 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +4118,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +4168,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4218,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4268,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,29 +4318,35 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>55100</v>
+      </c>
+      <c r="F89" s="3">
         <v>169200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>169100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>11100</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
@@ -3934,8 +4368,14 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,29 +4392,31 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-30800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-30800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-17900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-16500</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +4438,14 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4488,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,29 +4538,35 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-18400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-16900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-15600</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4128,8 +4588,14 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,29 +4612,31 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>56300</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>74600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>68600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
@@ -4190,8 +4658,14 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4708,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4758,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,29 +4808,35 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-56600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-56600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-74100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-68200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
@@ -4366,16 +4858,22 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-6100</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>4</v>
@@ -4410,29 +4908,35 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="F102" s="3">
         <v>88600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>88500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-85700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-78900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -4442,16 +4946,22 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
